--- a/DQN_sb3_framework_ste_实验结果_lx.xlsx
+++ b/DQN_sb3_framework_ste_实验结果_lx.xlsx
@@ -2055,7 +2055,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="80">
+  <fonts count="76">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2157,13 +2157,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="14"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -2254,14 +2247,6 @@
     </font>
     <font>
       <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="等线"/>
@@ -2273,12 +2258,6 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
@@ -2319,13 +2298,6 @@
     <font>
       <sz val="12"/>
       <name val="Arial"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="等线"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2502,25 +2474,13 @@
     <font>
       <vertAlign val="subscript"/>
       <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
       <name val="Cambria Math"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
+      <vertAlign val="subscript"/>
+      <sz val="9"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2531,11 +2491,18 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
       <sz val="9"/>
-      <color theme="1"/>
-      <name val="等线"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
       <charset val="134"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
@@ -2557,29 +2524,8 @@
       <charset val="134"/>
     </font>
     <font>
-      <vertAlign val="subscript"/>
       <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="9"/>
       <name val="Cambria Math"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <vertAlign val="subscript"/>
-      <sz val="9"/>
-      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -2594,8 +2540,34 @@
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <vertAlign val="subscript"/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="44">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2779,12 +2751,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -3174,152 +3140,152 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="44" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="40" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="13" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="45" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="46" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="46" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="13" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="47" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="47" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="48" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="48" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="49" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="49" fillId="14" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="50" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="50" fillId="15" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="51" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="51" fillId="15" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="52" fillId="16" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="52" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="53" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="53" fillId="14" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="15" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="55" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="55" fillId="15" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="56" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="56" fillId="16" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="57" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="57" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="58" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="59" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="60" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="59" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="63" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="58" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="62" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="63" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="130">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3410,13 +3376,13 @@
     <xf numFmtId="0" fontId="9" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3434,28 +3400,31 @@
     <xf numFmtId="0" fontId="10" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3464,7 +3433,7 @@
     <xf numFmtId="0" fontId="24" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3473,7 +3442,7 @@
     <xf numFmtId="0" fontId="24" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3485,28 +3454,25 @@
     <xf numFmtId="0" fontId="25" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="26" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
@@ -3518,94 +3484,85 @@
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="28" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="33" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="35" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3620,16 +3577,16 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3638,7 +3595,7 @@
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="36" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3656,43 +3613,40 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="29" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="41" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="35" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="38" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="39" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3701,13 +3655,13 @@
     <xf numFmtId="0" fontId="0" fillId="11" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -9764,328 +9718,328 @@
       <c r="G2" s="66"/>
     </row>
     <row r="3" s="58" customFormat="1" ht="40.8" customHeight="1" spans="1:1">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="58" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="4" s="59" customFormat="1" ht="43.8" customHeight="1" spans="1:10">
-      <c r="A4" s="68" t="s">
+      <c r="A4" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="68" t="s">
+      <c r="B4" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="C4" s="68" t="s">
+      <c r="C4" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="D4" s="68"/>
-      <c r="E4" s="69" t="s">
+      <c r="D4" s="67"/>
+      <c r="E4" s="68" t="s">
         <v>6</v>
       </c>
-      <c r="F4" s="69" t="s">
+      <c r="F4" s="68" t="s">
         <v>7</v>
       </c>
-      <c r="G4" s="70" t="s">
+      <c r="G4" s="69" t="s">
         <v>8</v>
       </c>
-      <c r="H4" s="70" t="s">
+      <c r="H4" s="69" t="s">
         <v>9</v>
       </c>
-      <c r="I4" s="70" t="s">
+      <c r="I4" s="69" t="s">
         <v>10</v>
       </c>
-      <c r="J4" s="112"/>
+      <c r="J4" s="109"/>
     </row>
     <row r="5" ht="18" spans="1:9">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="70" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="72" t="s">
+      <c r="B5" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="73" t="s">
+      <c r="C5" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="74"/>
-      <c r="E5" s="75"/>
-      <c r="F5" s="75"/>
-      <c r="G5" s="75"/>
-      <c r="H5" s="76"/>
-      <c r="I5" s="76"/>
+      <c r="D5" s="73"/>
+      <c r="E5" s="74"/>
+      <c r="F5" s="74"/>
+      <c r="G5" s="74"/>
+      <c r="H5" s="75"/>
+      <c r="I5" s="75"/>
     </row>
     <row r="6" ht="18" spans="1:9">
-      <c r="A6" s="71"/>
-      <c r="B6" s="72" t="s">
+      <c r="A6" s="70"/>
+      <c r="B6" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="73" t="s">
+      <c r="C6" s="72" t="s">
         <v>15</v>
       </c>
-      <c r="D6" s="74"/>
-      <c r="E6" s="75"/>
-      <c r="F6" s="75"/>
-      <c r="G6" s="75"/>
-      <c r="H6" s="76"/>
-      <c r="I6" s="76"/>
+      <c r="D6" s="73"/>
+      <c r="E6" s="74"/>
+      <c r="F6" s="74"/>
+      <c r="G6" s="74"/>
+      <c r="H6" s="75"/>
+      <c r="I6" s="75"/>
     </row>
     <row r="7" spans="1:9">
-      <c r="A7" s="77"/>
-      <c r="B7" s="72" t="s">
+      <c r="A7" s="76"/>
+      <c r="B7" s="71" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="73" t="s">
+      <c r="C7" s="72" t="s">
         <v>17</v>
       </c>
-      <c r="D7" s="74"/>
-      <c r="E7" s="75"/>
-      <c r="F7" s="75"/>
-      <c r="G7" s="75"/>
-      <c r="H7" s="75"/>
-      <c r="I7" s="75"/>
+      <c r="D7" s="73"/>
+      <c r="E7" s="74"/>
+      <c r="F7" s="74"/>
+      <c r="G7" s="74"/>
+      <c r="H7" s="74"/>
+      <c r="I7" s="74"/>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8" s="78" t="s">
+      <c r="A8" s="77" t="s">
         <v>18</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="71" t="s">
         <v>19</v>
       </c>
-      <c r="C8" s="73" t="s">
+      <c r="C8" s="72" t="s">
         <v>20</v>
       </c>
-      <c r="D8" s="74"/>
-      <c r="E8" s="75"/>
-      <c r="F8" s="75"/>
-      <c r="G8" s="75"/>
-      <c r="H8" s="75"/>
-      <c r="I8" s="75"/>
+      <c r="D8" s="73"/>
+      <c r="E8" s="74"/>
+      <c r="F8" s="74"/>
+      <c r="G8" s="74"/>
+      <c r="H8" s="74"/>
+      <c r="I8" s="74"/>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9" s="79"/>
-      <c r="B9" s="72" t="s">
+      <c r="A9" s="70"/>
+      <c r="B9" s="71" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="73" t="s">
+      <c r="C9" s="72" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="80"/>
-      <c r="E9" s="75"/>
-      <c r="F9" s="75"/>
-      <c r="G9" s="75"/>
-      <c r="H9" s="75"/>
-      <c r="I9" s="75"/>
+      <c r="D9" s="78"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10" s="79"/>
-      <c r="B10" s="72" t="s">
+      <c r="A10" s="70"/>
+      <c r="B10" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="C10" s="73" t="s">
+      <c r="C10" s="72" t="s">
         <v>24</v>
       </c>
-      <c r="D10" s="80"/>
-      <c r="E10" s="75"/>
-      <c r="F10" s="75"/>
-      <c r="G10" s="75"/>
-      <c r="H10" s="75"/>
-      <c r="I10" s="75"/>
+      <c r="D10" s="78"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="74"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="74"/>
+      <c r="I10" s="74"/>
     </row>
     <row r="11" spans="1:9">
-      <c r="A11" s="77"/>
-      <c r="B11" s="72" t="s">
+      <c r="A11" s="76"/>
+      <c r="B11" s="71" t="s">
         <v>25</v>
       </c>
-      <c r="C11" s="75" t="s">
+      <c r="C11" s="74" t="s">
         <v>26</v>
       </c>
-      <c r="D11" s="80"/>
-      <c r="E11" s="75"/>
-      <c r="F11" s="75"/>
-      <c r="G11" s="75"/>
-      <c r="H11" s="75"/>
-      <c r="I11" s="75"/>
+      <c r="D11" s="78"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
     </row>
     <row r="12" ht="17.4" spans="1:9">
-      <c r="A12" s="78" t="s">
+      <c r="A12" s="77" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="81" t="s">
+      <c r="B12" s="79" t="s">
         <v>28</v>
       </c>
-      <c r="C12" s="75"/>
-      <c r="D12" s="80"/>
-      <c r="E12" s="75"/>
-      <c r="F12" s="75"/>
-      <c r="G12" s="75"/>
-      <c r="H12" s="75"/>
-      <c r="I12" s="75"/>
+      <c r="C12" s="74"/>
+      <c r="D12" s="78"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
     </row>
     <row r="13" ht="17.4" spans="1:9">
-      <c r="A13" s="71"/>
-      <c r="B13" s="82" t="s">
+      <c r="A13" s="70"/>
+      <c r="B13" s="80" t="s">
         <v>29</v>
       </c>
-      <c r="C13" s="75"/>
-      <c r="D13" s="80"/>
-      <c r="E13" s="75"/>
-      <c r="F13" s="75"/>
-      <c r="G13" s="75"/>
-      <c r="H13" s="75"/>
-      <c r="I13" s="75"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="78"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
     </row>
     <row r="14" spans="1:9">
-      <c r="A14" s="71"/>
-      <c r="B14" s="72"/>
-      <c r="C14" s="75"/>
-      <c r="D14" s="80"/>
-      <c r="E14" s="75"/>
-      <c r="F14" s="75"/>
-      <c r="G14" s="75"/>
-      <c r="H14" s="75"/>
-      <c r="I14" s="75"/>
+      <c r="A14" s="70"/>
+      <c r="B14" s="71"/>
+      <c r="C14" s="74"/>
+      <c r="D14" s="78"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
     </row>
     <row r="15" spans="1:9">
-      <c r="A15" s="83"/>
-      <c r="B15" s="72"/>
-      <c r="C15" s="75"/>
-      <c r="D15" s="80"/>
-      <c r="E15" s="75"/>
-      <c r="F15" s="75"/>
-      <c r="G15" s="75"/>
-      <c r="H15" s="75"/>
-      <c r="I15" s="75"/>
+      <c r="A15" s="76"/>
+      <c r="B15" s="71"/>
+      <c r="C15" s="74"/>
+      <c r="D15" s="78"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" s="78" t="s">
+      <c r="A16" s="77" t="s">
         <v>30</v>
       </c>
-      <c r="B16" s="84" t="s">
+      <c r="B16" s="81" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="73" t="s">
+      <c r="C16" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="75"/>
-      <c r="F16" s="75"/>
-      <c r="G16" s="75"/>
-      <c r="H16" s="75"/>
-      <c r="I16" s="75"/>
+      <c r="D16" s="78"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" s="71"/>
-      <c r="B17" s="72" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="71" t="s">
         <v>33</v>
       </c>
-      <c r="C17" s="73"/>
-      <c r="D17" s="80"/>
-      <c r="E17" s="75"/>
-      <c r="F17" s="75"/>
-      <c r="G17" s="75"/>
-      <c r="H17" s="75"/>
-      <c r="I17" s="75"/>
+      <c r="C17" s="72"/>
+      <c r="D17" s="78"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
     </row>
     <row r="18" spans="1:9">
-      <c r="A18" s="71"/>
-      <c r="B18" s="84" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="81" t="s">
         <v>34</v>
       </c>
-      <c r="C18" s="73"/>
-      <c r="D18" s="80"/>
-      <c r="E18" s="75"/>
-      <c r="F18" s="75"/>
-      <c r="G18" s="75"/>
-      <c r="H18" s="75"/>
-      <c r="I18" s="75"/>
+      <c r="C18" s="72"/>
+      <c r="D18" s="78"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" s="77"/>
-      <c r="B19" s="84" t="s">
+      <c r="A19" s="76"/>
+      <c r="B19" s="81" t="s">
         <v>35</v>
       </c>
-      <c r="C19" s="73" t="s">
+      <c r="C19" s="72" t="s">
         <v>32</v>
       </c>
-      <c r="D19" s="80"/>
-      <c r="E19" s="75"/>
-      <c r="F19" s="75"/>
-      <c r="G19" s="75"/>
-      <c r="H19" s="75"/>
-      <c r="I19" s="75"/>
+      <c r="D19" s="78"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
     </row>
     <row r="20" ht="17.4" spans="1:9">
-      <c r="A20" s="78" t="s">
+      <c r="A20" s="77" t="s">
         <v>36</v>
       </c>
-      <c r="B20" s="81" t="s">
+      <c r="B20" s="79" t="s">
         <v>37</v>
       </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="80"/>
-      <c r="E20" s="75"/>
-      <c r="F20" s="75"/>
-      <c r="G20" s="75"/>
-      <c r="H20" s="75"/>
-      <c r="I20" s="75"/>
+      <c r="C20" s="74"/>
+      <c r="D20" s="78"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" spans="1:9">
-      <c r="A21" s="77"/>
-      <c r="B21" s="72"/>
-      <c r="C21" s="75"/>
-      <c r="D21" s="80"/>
-      <c r="E21" s="75"/>
-      <c r="F21" s="75"/>
-      <c r="G21" s="75"/>
-      <c r="H21" s="75"/>
-      <c r="I21" s="75"/>
+      <c r="A21" s="76"/>
+      <c r="B21" s="71"/>
+      <c r="C21" s="74"/>
+      <c r="D21" s="78"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" s="78" t="s">
+      <c r="A22" s="77" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="C22" s="73" t="s">
+      <c r="C22" s="72" t="s">
         <v>40</v>
       </c>
-      <c r="D22" s="80"/>
-      <c r="E22" s="75"/>
-      <c r="F22" s="75"/>
-      <c r="G22" s="75"/>
-      <c r="H22" s="75"/>
-      <c r="I22" s="75"/>
+      <c r="D22" s="78"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="71"/>
-      <c r="B23" s="72"/>
-      <c r="C23" s="75"/>
-      <c r="D23" s="80"/>
-      <c r="E23" s="75"/>
-      <c r="F23" s="75"/>
-      <c r="G23" s="75"/>
-      <c r="H23" s="75"/>
-      <c r="I23" s="75"/>
+      <c r="A23" s="70"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="74"/>
+      <c r="D23" s="78"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" s="83"/>
-      <c r="B24" s="72"/>
-      <c r="C24" s="75"/>
-      <c r="D24" s="80"/>
-      <c r="E24" s="75"/>
-      <c r="F24" s="75"/>
-      <c r="G24" s="75"/>
-      <c r="H24" s="75"/>
-      <c r="I24" s="75"/>
+      <c r="A24" s="76"/>
+      <c r="B24" s="71"/>
+      <c r="C24" s="74"/>
+      <c r="D24" s="78"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
     </row>
     <row r="25" spans="4:4">
-      <c r="D25" s="80"/>
+      <c r="D25" s="78"/>
     </row>
     <row r="26" spans="4:4">
-      <c r="D26" s="80"/>
+      <c r="D26" s="78"/>
     </row>
     <row r="27" spans="4:4">
-      <c r="D27" s="80"/>
+      <c r="D27" s="78"/>
     </row>
     <row r="29" s="58" customFormat="1" spans="1:1">
       <c r="A29" s="58" t="s">
@@ -10094,7 +10048,7 @@
     </row>
     <row r="30" s="56" customFormat="1"/>
     <row r="31" s="56" customFormat="1" spans="1:1">
-      <c r="A31" s="85" t="s">
+      <c r="A31" s="82" t="s">
         <v>42</v>
       </c>
     </row>
@@ -10105,10 +10059,10 @@
       <c r="B32" t="s">
         <v>44</v>
       </c>
-      <c r="C32" s="86" t="s">
+      <c r="C32" s="83" t="s">
         <v>45</v>
       </c>
-      <c r="D32" s="86"/>
+      <c r="D32" s="83"/>
     </row>
     <row r="33" spans="1:2">
       <c r="A33" s="56" t="s">
@@ -10127,7 +10081,7 @@
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" s="87" t="s">
+      <c r="A36" s="84" t="s">
         <v>50</v>
       </c>
     </row>
@@ -10143,167 +10097,167 @@
       <c r="A38" s="56"/>
     </row>
     <row r="39" ht="16.35" spans="1:8">
-      <c r="A39" s="88" t="s">
+      <c r="A39" s="85" t="s">
         <v>52</v>
       </c>
-      <c r="B39" s="89"/>
-      <c r="C39" s="89"/>
-      <c r="D39" s="89"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="90"/>
+      <c r="B39" s="86"/>
+      <c r="C39" s="86"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="86"/>
+      <c r="F39" s="86"/>
+      <c r="G39" s="87"/>
       <c r="H39" s="38" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="91" t="s">
+    <row r="40" ht="16.35" spans="1:7">
+      <c r="A40" s="88" t="s">
         <v>54</v>
       </c>
-      <c r="B40" s="88" t="s">
+      <c r="B40" s="85" t="s">
         <v>55</v>
       </c>
-      <c r="C40" s="90"/>
-      <c r="D40" s="92" t="s">
+      <c r="C40" s="87"/>
+      <c r="D40" s="89" t="s">
         <v>16</v>
       </c>
-      <c r="E40" s="93" t="s">
+      <c r="E40" s="90" t="s">
         <v>4</v>
       </c>
-      <c r="F40" s="92" t="s">
+      <c r="F40" s="89" t="s">
         <v>56</v>
       </c>
-      <c r="G40" s="94" t="s">
+      <c r="G40" s="91" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="41" ht="16.35" spans="1:7">
-      <c r="A41" s="95"/>
-      <c r="B41" s="92" t="s">
+      <c r="A41" s="92"/>
+      <c r="B41" s="89" t="s">
         <v>58</v>
       </c>
-      <c r="C41" s="93">
+      <c r="C41" s="90">
         <v>1</v>
       </c>
-      <c r="D41" s="96">
+      <c r="D41" s="93">
         <v>1</v>
       </c>
-      <c r="E41" s="93" t="s">
+      <c r="E41" s="90" t="s">
         <v>59</v>
       </c>
-      <c r="F41" s="97"/>
-      <c r="G41" s="97"/>
+      <c r="F41" s="94"/>
+      <c r="G41" s="94"/>
     </row>
     <row r="42" ht="23.55" spans="1:7">
-      <c r="A42" s="95"/>
-      <c r="B42" s="92" t="s">
+      <c r="A42" s="92"/>
+      <c r="B42" s="89" t="s">
         <v>60</v>
       </c>
-      <c r="C42" s="93">
+      <c r="C42" s="90">
         <v>1</v>
       </c>
-      <c r="D42" s="98"/>
-      <c r="E42" s="93" t="s">
+      <c r="D42" s="95"/>
+      <c r="E42" s="90" t="s">
         <v>61</v>
       </c>
-      <c r="F42" s="99"/>
-      <c r="G42" s="99"/>
+      <c r="F42" s="96"/>
+      <c r="G42" s="96"/>
     </row>
     <row r="43" ht="23.55" spans="1:13">
-      <c r="A43" s="100"/>
-      <c r="B43" s="101" t="s">
+      <c r="A43" s="97"/>
+      <c r="B43" s="98" t="s">
         <v>62</v>
       </c>
-      <c r="C43" s="98"/>
-      <c r="D43" s="98"/>
-      <c r="E43" s="98"/>
-      <c r="F43" s="102"/>
-      <c r="G43" s="102"/>
-      <c r="I43" s="111"/>
-      <c r="J43" s="80"/>
-      <c r="K43" s="111"/>
-      <c r="L43" s="80"/>
-      <c r="M43" s="111"/>
+      <c r="C43" s="95"/>
+      <c r="D43" s="95"/>
+      <c r="E43" s="95"/>
+      <c r="F43" s="99"/>
+      <c r="G43" s="99"/>
+      <c r="I43" s="108"/>
+      <c r="J43" s="78"/>
+      <c r="K43" s="108"/>
+      <c r="L43" s="78"/>
+      <c r="M43" s="108"/>
     </row>
     <row r="44" ht="22.8" spans="1:13">
-      <c r="A44" s="103"/>
-      <c r="B44" s="104"/>
-      <c r="C44" s="104"/>
-      <c r="D44" s="104"/>
-      <c r="E44" s="105"/>
-      <c r="F44" s="104"/>
-      <c r="G44" s="105"/>
-      <c r="H44" s="80"/>
-      <c r="I44" s="111"/>
-      <c r="J44" s="80"/>
-      <c r="K44" s="111"/>
-      <c r="L44" s="80"/>
-      <c r="M44" s="111"/>
+      <c r="A44" s="100"/>
+      <c r="B44" s="101"/>
+      <c r="C44" s="101"/>
+      <c r="D44" s="101"/>
+      <c r="E44" s="102"/>
+      <c r="F44" s="101"/>
+      <c r="G44" s="102"/>
+      <c r="H44" s="78"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="78"/>
+      <c r="K44" s="108"/>
+      <c r="L44" s="78"/>
+      <c r="M44" s="108"/>
     </row>
     <row r="45" ht="22.8" spans="1:13">
-      <c r="A45" s="103"/>
-      <c r="B45" s="104"/>
-      <c r="C45" s="104"/>
-      <c r="D45" s="104"/>
-      <c r="E45" s="105"/>
-      <c r="F45" s="104"/>
-      <c r="G45" s="105"/>
-      <c r="H45" s="80"/>
-      <c r="I45" s="111"/>
-      <c r="J45" s="80"/>
-      <c r="K45" s="111"/>
-      <c r="L45" s="80"/>
-      <c r="M45" s="111"/>
+      <c r="A45" s="100"/>
+      <c r="B45" s="101"/>
+      <c r="C45" s="101"/>
+      <c r="D45" s="101"/>
+      <c r="E45" s="102"/>
+      <c r="F45" s="101"/>
+      <c r="G45" s="102"/>
+      <c r="H45" s="78"/>
+      <c r="I45" s="108"/>
+      <c r="J45" s="78"/>
+      <c r="K45" s="108"/>
+      <c r="L45" s="78"/>
+      <c r="M45" s="108"/>
     </row>
     <row r="46" ht="22.8" spans="1:13">
-      <c r="A46" s="103"/>
-      <c r="B46" s="104"/>
-      <c r="C46" s="104"/>
-      <c r="D46" s="104"/>
-      <c r="E46" s="105"/>
-      <c r="F46" s="104"/>
-      <c r="G46" s="105"/>
-      <c r="H46" s="80"/>
-      <c r="I46" s="111"/>
-      <c r="J46" s="80"/>
-      <c r="K46" s="111"/>
-      <c r="L46" s="80"/>
-      <c r="M46" s="111"/>
+      <c r="A46" s="100"/>
+      <c r="B46" s="101"/>
+      <c r="C46" s="101"/>
+      <c r="D46" s="101"/>
+      <c r="E46" s="102"/>
+      <c r="F46" s="101"/>
+      <c r="G46" s="102"/>
+      <c r="H46" s="78"/>
+      <c r="I46" s="108"/>
+      <c r="J46" s="78"/>
+      <c r="K46" s="108"/>
+      <c r="L46" s="78"/>
+      <c r="M46" s="108"/>
     </row>
     <row r="47" s="60" customFormat="1" ht="22.8" spans="1:13">
-      <c r="A47" s="106"/>
-      <c r="B47" s="107"/>
-      <c r="C47" s="107"/>
-      <c r="D47" s="107"/>
-      <c r="E47" s="108"/>
-      <c r="F47" s="107"/>
-      <c r="G47" s="108"/>
-      <c r="H47" s="109"/>
-      <c r="I47" s="113"/>
-      <c r="J47" s="109"/>
-      <c r="K47" s="113"/>
-      <c r="L47" s="109"/>
-      <c r="M47" s="113"/>
+      <c r="A47" s="103"/>
+      <c r="B47" s="104"/>
+      <c r="C47" s="104"/>
+      <c r="D47" s="104"/>
+      <c r="E47" s="105"/>
+      <c r="F47" s="104"/>
+      <c r="G47" s="105"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="110"/>
+      <c r="J47" s="106"/>
+      <c r="K47" s="110"/>
+      <c r="L47" s="106"/>
+      <c r="M47" s="110"/>
     </row>
     <row r="48" spans="1:13">
-      <c r="A48" s="110" t="s">
+      <c r="A48" s="107" t="s">
         <v>63</v>
       </c>
-      <c r="B48" s="80"/>
-      <c r="C48" s="111"/>
-      <c r="D48" s="111"/>
-      <c r="E48" s="80"/>
-      <c r="F48" s="111"/>
-      <c r="G48" s="80"/>
-      <c r="H48" s="80"/>
-      <c r="I48" s="111"/>
-      <c r="J48" s="80"/>
-      <c r="K48" s="111"/>
-      <c r="L48" s="80"/>
-      <c r="M48" s="111"/>
+      <c r="B48" s="78"/>
+      <c r="C48" s="108"/>
+      <c r="D48" s="108"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="108"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="108"/>
+      <c r="J48" s="78"/>
+      <c r="K48" s="108"/>
+      <c r="L48" s="78"/>
+      <c r="M48" s="108"/>
     </row>
     <row r="50" s="58" customFormat="1" spans="1:1">
-      <c r="A50" s="67" t="s">
+      <c r="A50" s="58" t="s">
         <v>64</v>
       </c>
     </row>
@@ -10313,191 +10267,191 @@
       </c>
     </row>
     <row r="67" s="61" customFormat="1" spans="1:2">
-      <c r="A67" s="114" t="s">
+      <c r="A67" s="111" t="s">
         <v>66</v>
       </c>
-      <c r="B67" s="115"/>
+      <c r="B67" s="111"/>
     </row>
     <row r="68" s="56" customFormat="1" spans="1:1">
-      <c r="A68" s="116" t="s">
+      <c r="A68" s="112" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="69" s="62" customFormat="1" ht="22.8" customHeight="1" spans="1:15">
-      <c r="A69" s="78" t="s">
+      <c r="A69" s="77" t="s">
         <v>68</v>
       </c>
-      <c r="B69" s="78" t="s">
+      <c r="B69" s="77" t="s">
         <v>69</v>
       </c>
-      <c r="C69" s="117" t="s">
+      <c r="C69" s="113" t="s">
         <v>57</v>
       </c>
-      <c r="D69" s="118" t="s">
+      <c r="D69" s="114" t="s">
         <v>70</v>
       </c>
-      <c r="E69" s="119"/>
-      <c r="F69" s="119"/>
-      <c r="G69" s="119"/>
-      <c r="H69" s="119"/>
-      <c r="I69" s="119"/>
-      <c r="J69" s="119"/>
-      <c r="K69" s="119"/>
-      <c r="L69" s="119"/>
-      <c r="M69" s="119"/>
-      <c r="N69" s="119"/>
-      <c r="O69" s="129"/>
+      <c r="E69" s="115"/>
+      <c r="F69" s="115"/>
+      <c r="G69" s="115"/>
+      <c r="H69" s="115"/>
+      <c r="I69" s="115"/>
+      <c r="J69" s="115"/>
+      <c r="K69" s="115"/>
+      <c r="L69" s="115"/>
+      <c r="M69" s="115"/>
+      <c r="N69" s="115"/>
+      <c r="O69" s="125"/>
     </row>
     <row r="70" s="63" customFormat="1" ht="46.8" spans="1:4">
-      <c r="A70" s="71"/>
-      <c r="B70" s="71"/>
-      <c r="C70" s="120"/>
+      <c r="A70" s="70"/>
+      <c r="B70" s="70"/>
+      <c r="C70" s="116"/>
       <c r="D70" s="63" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="71" s="63" customFormat="1" ht="40.2" customHeight="1" spans="1:4">
-      <c r="A71" s="83"/>
-      <c r="B71" s="83"/>
-      <c r="C71" s="121"/>
-      <c r="D71" s="122" t="s">
+      <c r="A71" s="76"/>
+      <c r="B71" s="76"/>
+      <c r="C71" s="117"/>
+      <c r="D71" s="118" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="72" s="64" customFormat="1" spans="1:2">
-      <c r="A72" s="123" t="s">
+      <c r="A72" s="119" t="s">
         <v>73</v>
       </c>
-      <c r="B72" s="124" t="s">
+      <c r="B72" s="120" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="73" s="64" customFormat="1" spans="1:2">
-      <c r="A73" s="125"/>
-      <c r="B73" s="124" t="s">
+      <c r="A73" s="121"/>
+      <c r="B73" s="120" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="74" s="64" customFormat="1" spans="1:2">
-      <c r="A74" s="125"/>
-      <c r="B74" s="124" t="s">
+      <c r="A74" s="121"/>
+      <c r="B74" s="120" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="75" s="64" customFormat="1" spans="1:2">
-      <c r="A75" s="125"/>
-      <c r="B75" s="124" t="s">
+      <c r="A75" s="121"/>
+      <c r="B75" s="120" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="76" s="64" customFormat="1" spans="1:2">
-      <c r="A76" s="125"/>
-      <c r="B76" s="124" t="s">
+      <c r="A76" s="121"/>
+      <c r="B76" s="120" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="77" s="64" customFormat="1" spans="1:2">
-      <c r="A77" s="125"/>
-      <c r="B77" s="124" t="s">
+      <c r="A77" s="121"/>
+      <c r="B77" s="120" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="78" s="64" customFormat="1" spans="1:2">
-      <c r="A78" s="125"/>
-      <c r="B78" s="124" t="s">
+      <c r="A78" s="121"/>
+      <c r="B78" s="120" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="79" s="64" customFormat="1" spans="1:4">
-      <c r="A79" s="125"/>
-      <c r="B79" s="124" t="s">
+      <c r="A79" s="121"/>
+      <c r="B79" s="120" t="s">
         <v>79</v>
       </c>
-      <c r="C79" s="126"/>
-      <c r="D79" s="126"/>
+      <c r="C79" s="122"/>
+      <c r="D79" s="122"/>
     </row>
     <row r="80" s="64" customFormat="1" spans="1:2">
-      <c r="A80" s="125"/>
-      <c r="B80" s="124" t="s">
+      <c r="A80" s="121"/>
+      <c r="B80" s="120" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="81" s="64" customFormat="1" spans="1:2">
-      <c r="A81" s="125"/>
-      <c r="B81" s="124" t="s">
+      <c r="A81" s="121"/>
+      <c r="B81" s="120" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="82" s="64" customFormat="1" spans="1:2">
-      <c r="A82" s="125"/>
-      <c r="B82" s="124" t="s">
+      <c r="A82" s="121"/>
+      <c r="B82" s="120" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="83" s="64" customFormat="1" spans="1:2">
-      <c r="A83" s="125"/>
-      <c r="B83" s="124" t="s">
+      <c r="A83" s="121"/>
+      <c r="B83" s="120" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="84" s="64" customFormat="1" spans="1:2">
-      <c r="A84" s="125"/>
-      <c r="B84" s="124" t="s">
+      <c r="A84" s="121"/>
+      <c r="B84" s="120" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="85" s="65" customFormat="1" spans="1:2">
-      <c r="A85" s="127" t="s">
+      <c r="A85" s="123" t="s">
         <v>85</v>
       </c>
       <c r="B85"/>
     </row>
     <row r="86" s="65" customFormat="1" spans="1:2">
-      <c r="A86" s="128"/>
+      <c r="A86" s="124"/>
       <c r="B86"/>
     </row>
     <row r="87" s="65" customFormat="1" spans="1:2">
-      <c r="A87" s="128"/>
+      <c r="A87" s="124"/>
       <c r="B87"/>
     </row>
     <row r="88" s="65" customFormat="1" spans="1:2">
-      <c r="A88" s="128"/>
+      <c r="A88" s="124"/>
       <c r="B88"/>
     </row>
     <row r="89" s="65" customFormat="1" spans="1:2">
-      <c r="A89" s="128"/>
+      <c r="A89" s="124"/>
       <c r="B89"/>
     </row>
     <row r="90" s="65" customFormat="1" spans="1:2">
-      <c r="A90" s="128"/>
+      <c r="A90" s="124"/>
       <c r="B90"/>
     </row>
     <row r="91" s="65" customFormat="1" spans="1:2">
-      <c r="A91" s="128"/>
+      <c r="A91" s="124"/>
       <c r="B91"/>
     </row>
     <row r="92" s="65" customFormat="1" spans="1:2">
-      <c r="A92" s="128"/>
+      <c r="A92" s="124"/>
       <c r="B92"/>
     </row>
     <row r="93" s="65" customFormat="1" spans="1:2">
-      <c r="A93" s="128"/>
+      <c r="A93" s="124"/>
       <c r="B93"/>
     </row>
     <row r="94" s="65" customFormat="1" spans="1:2">
-      <c r="A94" s="128"/>
+      <c r="A94" s="124"/>
       <c r="B94"/>
     </row>
     <row r="95" s="65" customFormat="1" spans="1:2">
-      <c r="A95" s="128"/>
+      <c r="A95" s="124"/>
       <c r="B95"/>
     </row>
     <row r="96" s="65" customFormat="1" spans="1:2">
-      <c r="A96" s="128"/>
+      <c r="A96" s="124"/>
       <c r="B96"/>
     </row>
     <row r="97" s="65" customFormat="1" spans="1:2">
-      <c r="A97" s="128"/>
+      <c r="A97" s="124"/>
       <c r="B97"/>
     </row>
     <row r="99" s="5" customFormat="1" spans="1:1">
